--- a/product-template.xlsx
+++ b/product-template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,7 +29,7 @@
     <font>
       <name val="Meiryo UI"/>
       <b val="1"/>
-      <color rgb="0017442F"/>
+      <color rgb="008A3B00"/>
     </font>
     <font>
       <name val="Meiryo UI"/>
@@ -40,13 +40,23 @@
     <font>
       <name val="Meiryo UI"/>
     </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="0017442F"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE8CC"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -80,22 +90,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -463,76 +477,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K301"/>
+  <dimension ref="A1:H301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" style="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" style="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>メーカー</t>
+          <t>メーカー ※必須</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>商品名</t>
+          <t>商品名 ※必須</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>規格</t>
+          <t>規格 ※必須</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>JAN</t>
+          <t>JAN ※必須</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>入数</t>
+          <t>入数 ※必須</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>原価（本体）</t>
+          <t>原価（本体） ※必須</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>原価（総額）</t>
+          <t>売価（本体） ※必須</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>売価（本体）</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>売価（総額）</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>値入率</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>別名</t>
+          <t>締切（何日前） ※必須</t>
         </is>
       </c>
     </row>
@@ -1437,6 +1433,25 @@
       <c r="D301" s="1" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="5">
+    <dataValidation sqref="D2:D301" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="JAN" error="数字だけ・8〜13けたで入れてください（JAN の無い商品は空のまま）。" type="textLength" operator="between">
+      <formula1>8</formula1>
+      <formula2>13</formula2>
+    </dataValidation>
+    <dataValidation sqref="E2:E301" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入数" error="1 以上の整数で入れてください。" type="whole" operator="greaterThanOrEqual">
+      <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F301" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="原価（本体）" error="0 より大きい数で入れてください（円）。" type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G301" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="売価（本体）" error="0 より大きい数で入れてください（円）。" type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H301" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="締切（何日前）" error="0 から 30 の整数で入れてください（例 2 なら、11/1 着は 10/30 12:00 まで）。" promptTitle="締切（何日前）※必須" prompt="着く日の何日前の 12:00 で締め切るか（0〜30）" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>30</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1447,20 +1462,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1480,395 +1492,334 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>・この「書き方」のシートは読み込みません（上の記入例も読み込みません）。</t>
+          <t>・8つとも書いてください。商品名と締切（何日前）が空の行は登録できません。ほかが空でも登録はできますが、あとで埋めてください。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>・「更新」になるのは、JAN が同じ商品です。JAN が空なら、商品名と規格が同じ商品です（全角・半角、カタカナ・ひらがな、空白の違いは同じとみなします）。</t>
+          <t>・書いてある値の形が違うと、その行は登録できません（JAN＝数字だけ 8〜13けた・入数＝1以上の整数・原価／売価＝0 より大きい数・締切＝0〜30 の整数）。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>・JAN が新しくても、JAN の無い同じ商品名・規格の商品があれば、その商品に JAN を入れます。どれにも当たらなければ「新規」です。</t>
+          <t>・税込（総額）と値入率は書きません（原価・売価の本体から、登録すると自動で計算します）。探すときの読み（別名）は、画面の「商品マスター」で入れます。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>・空の欄は、いまの値のままです（消したいときは、画面の「商品マスター」で1件ずつ直します）。</t>
+          <t>・この「書き方」のシートは読み込みません（下の記入例も読み込みません）。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>・1回に300行まで。エラーが1つでもあると登録できません。確かめの表の理由を見て直し、もう一度アップロードしてください。</t>
+          <t>・「更新」になるのは、JAN が同じ商品です。JAN が空なら、商品名と規格が同じ商品です（全角・半角、カタカナ・ひらがな、空白の違いは同じとみなします）。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>・JAN が新しくても、JAN の無い同じ商品名・規格の商品があれば、その商品に JAN を入れます。どれにも当たらなければ「新規」です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>・すでにある商品の行（更新）で空の欄は、いまの値のままです（消したいときは、画面の「商品マスター」で1件ずつ直します）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>・1回に300行まで。エラーが1つでもあると登録できません。確かめの表の理由を見て直し、もう一度アップロードしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>・新しい商品は、選んでいる月の注文書にも入れられます（確かめの表の印で選べます）。</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>列</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>書くこと</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>記入例</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>メーカー</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>空でもよい（120文字まで）</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>見本ミート</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>商品名</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>必ず書く（120文字まで）</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>【見本】豚バラうす切り</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>規格</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>空でもよい（120文字まで）。例 500g・1kg</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>500g</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>数字だけ。空でもよい。この列は文字の書式なので、先頭の0もそのまま書けます。ほかの表から貼るときは「値だけ貼り付け」にしてください</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>0490000000017</t>
+          <t>メーカー ※必須</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>書く（120文字まで）。空でも登録はできますが、あとで埋めてください</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>見本ミート</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>入数</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>1ケースの個数（数）</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>商品名 ※必須</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>必ず書く（120文字まで）。空の行は登録できません</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>【見本】豚バラうす切り</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>原価（本体）</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>円（数）</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>480</t>
+          <t>規格 ※必須</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>書く（120文字まで）。例 500g・1kg。空でも登録はできますが、あとで埋めてください</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>500g</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>原価（総額）</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>税込の円。空でよい（空なら 本体×1.08 の端数切り捨て＝480 → 518 が入ります）</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>（空）</t>
+          <t>JAN ※必須</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>数字だけ・8〜13けた。この列は文字の書式なので、先頭の0もそのまま書けます。ほかの表から貼るときは「値だけ貼り付け」に。JAN の無い商品は空でも登録できます</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>0490000000017</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>売価（本体）</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>円（数）</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>598</t>
+          <t>入数 ※必須</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1ケースの個数（1以上の整数）。空でも登録はできますが、あとで埋めてください</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>売価（総額）</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>税込の円。空でよい（空なら 本体×1.08 の端数切り捨て＝598 → 645 が入ります）</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>（空）</t>
+          <t>原価（本体） ※必須</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>円（0 より大きい数）。税込（総額）と値入率は、登録すると自動で計算します</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>480</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>値入率</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>0.29 でも 29（%）でもよい。空でよい（空なら（売価本体−原価本体）÷売価本体＝0.1973 が入ります）</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>（空）</t>
+          <t>売価（本体） ※必須</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>円（0 より大きい数）</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>598</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>別名</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>探すときの読み・別の呼び名。いくつかあるときは「、」で区切る</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>ぶたばら、豚三枚肉</t>
+          <t>締切（何日前） ※必須</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>必ず書く。着く日の何日前の 12:00 で、店の注文を締め切るか（0〜30 の整数）。例 2 なら、11/1 着は 10/30 12:00 まで店が直せる。空の行は登録できません</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>記入例（「入力」には、この形で書きます。ここは読み込みません）</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>メーカー</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>商品名</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>規格</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>入数</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>原価（本体）</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>原価（総額）</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>売価（本体）</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>売価（総額）</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>値入率</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>別名</t>
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>メーカー ※必須</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>商品名 ※必須</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>規格 ※必須</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>JAN ※必須</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>入数 ※必須</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>原価（本体） ※必須</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>売価（本体） ※必須</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>締切（何日前） ※必須</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>見本ミート</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>【見本】豚バラうす切り</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>500g</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>0490000000017</t>
         </is>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="11" t="n">
         <v>480</v>
       </c>
-      <c r="G26" s="9" t="n"/>
-      <c r="H26" s="9" t="n">
+      <c r="G26" s="11" t="n">
         <v>598</v>
       </c>
-      <c r="I26" s="9" t="n"/>
-      <c r="J26" s="9" t="n"/>
-      <c r="K26" s="9" t="inlineStr">
-        <is>
-          <t>ぶたばら、豚三枚肉</t>
-        </is>
+      <c r="H26" s="11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>見本チキン</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>【見本】若鶏もも正肉</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>2kg</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>0490000000024</t>
         </is>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="11" t="n">
         <v>1200</v>
       </c>
-      <c r="G27" s="9" t="n">
-        <v>1296</v>
-      </c>
-      <c r="H27" s="9" t="n">
+      <c r="G27" s="11" t="n">
         <v>1480</v>
       </c>
-      <c r="I27" s="9" t="n">
-        <v>1598</v>
-      </c>
-      <c r="J27" s="9" t="n">
-        <v>0.189</v>
-      </c>
-      <c r="K27" s="9" t="inlineStr">
-        <is>
-          <t>とりもも</t>
-        </is>
+      <c r="H27" s="11" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/product-template.xlsx
+++ b/product-template.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H301"/>
+  <dimension ref="A1:I301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -488,6 +488,7 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -531,6 +532,11 @@
           <t>締切（何日前） ※必須</t>
         </is>
       </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>発注区分 ※必須</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="D2" s="1" t="n"/>
@@ -1433,7 +1439,7 @@
       <c r="D301" s="1" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation sqref="D2:D301" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="JAN" error="数字だけ・8〜13けたで入れてください（JAN の無い商品は空のまま）。" type="textLength" operator="between">
       <formula1>8</formula1>
       <formula2>13</formula2>
@@ -1451,6 +1457,9 @@
       <formula1>0</formula1>
       <formula2>30</formula2>
     </dataValidation>
+    <dataValidation sqref="I2:I301" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="発注区分" error="「通常発注」か「集約発注」を選んでください。" promptTitle="発注区分※必須" prompt="通常発注／集約発注（BY が集めて振り分ける）から選ぶ" type="list">
+      <formula1>"通常発注,集約発注"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1462,7 +1471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1473,6 +1482,7 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1492,14 +1502,14 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>・8つとも書いてください。商品名と締切（何日前）が空の行は登録できません。ほかが空でも登録はできますが、あとで埋めてください。</t>
+          <t>・9つとも書いてください。商品名と締切（何日前）が空の行は登録できません。ほかが空でも登録はできますが、あとで埋めてください（発注区分が空の新しい商品は「通常発注」になります）。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>・書いてある値の形が違うと、その行は登録できません（JAN＝数字だけ 8〜13けた・入数＝1以上の整数・原価／売価＝0 より大きい数・締切＝0〜30 の整数）。</t>
+          <t>・書いてある値の形が違うと、その行は登録できません（JAN＝数字だけ 8〜13けた・入数＝1以上の整数・原価／売価＝0 より大きい数・締切＝0〜30 の整数・発注区分＝通常発注か集約発注）。</t>
         </is>
       </c>
     </row>
@@ -1705,121 +1715,153 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>発注区分 ※必須</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>「通常発注」か「集約発注」を選ぶ（欄を押すと選べます）。集約発注＝BY が集めて振り分ける商品で、締切の後、BY が「確定する」を押すまで確定しません。新しい商品で空なら「通常発注」になります（黄色の注意）</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>通常発注</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>記入例（「入力」には、この形で書きます。ここは読み込みません）</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>メーカー ※必須</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>商品名 ※必須</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>規格 ※必須</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>JAN ※必須</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>入数 ※必須</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>原価（本体） ※必須</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>売価（本体） ※必須</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>締切（何日前） ※必須</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>見本ミート</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>【見本】豚バラうす切り</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>500g</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>0490000000017</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="F26" s="11" t="n">
-        <v>480</v>
-      </c>
-      <c r="G26" s="11" t="n">
-        <v>598</v>
-      </c>
-      <c r="H26" s="11" t="n">
-        <v>2</v>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>発注区分 ※必須</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
+          <t>見本ミート</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>【見本】豚バラうす切り</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>0490000000017</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>480</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>598</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>通常発注</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
           <t>見本チキン</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>【見本】若鶏もも正肉</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>2kg</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>0490000000024</t>
         </is>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E28" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F28" s="11" t="n">
         <v>1200</v>
       </c>
-      <c r="G27" s="11" t="n">
+      <c r="G28" s="11" t="n">
         <v>1480</v>
       </c>
-      <c r="H27" s="11" t="n">
+      <c r="H28" s="11" t="n">
         <v>3</v>
+      </c>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>集約発注</t>
+        </is>
       </c>
     </row>
   </sheetData>
